--- a/data/trans_orig/KIDMED_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R2-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,92 +735,92 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3828</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1578</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122255</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119480</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>113523</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>110524</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>117842</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>114770</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>118598</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>135964</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133049</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136815</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>249488</t>
+          <t>240097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246054</t>
+          <t>236821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>227535</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>223758</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>229888</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>184786</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>182482</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243137</t>
+          <t>179359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>238530</t>
+          <t>176934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246006</t>
+          <t>180271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>427922</t>
+          <t>406893</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422280</t>
+          <t>401858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430765</t>
+          <t>409431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11681</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18886</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5424</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10466</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154841</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147636</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159843</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182825</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177783</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186022</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>170436</t>
+          <t>149283</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162238</t>
+          <t>144198</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175691</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>353262</t>
+          <t>304124</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>343280</t>
+          <t>294837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360169</t>
+          <t>310454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6342</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13781</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9074</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4723</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14941</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159823</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152384</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>155445</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149578</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159796</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>170666</t>
+          <t>154474</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163336</t>
+          <t>148091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174428</t>
+          <t>159136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326111</t>
+          <t>314297</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>316873</t>
+          <t>305262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332332</t>
+          <t>319964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>664453</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655166</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>672435</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>636580</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>628230</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>641959</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>720203</t>
+          <t>600959</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>709203</t>
+          <t>592983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728451</t>
+          <t>606975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1356783</t>
+          <t>1265411</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1343607</t>
+          <t>1252529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1367375</t>
+          <t>1275589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
